--- a/metrics.xlsx
+++ b/metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="36">
   <si>
     <t xml:space="preserve">Scene</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">VMAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMOS</t>
   </si>
   <si>
     <t xml:space="preserve">antique</t>
@@ -320,7 +317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U65"/>
+  <dimension ref="A1:T65"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.31"/>
@@ -387,16 +384,13 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>0.974087493181229</v>
@@ -452,16 +446,13 @@
       <c r="T2" s="0" t="n">
         <v>69.114165044</v>
       </c>
-      <c r="U2" s="0" t="n">
-        <v>4.30852</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>0.974344435453415</v>
@@ -517,16 +508,13 @@
       <c r="T3" s="0" t="n">
         <v>69.236252616</v>
       </c>
-      <c r="U3" s="0" t="n">
-        <v>4.4578</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>0.972583393096924</v>
@@ -582,16 +570,13 @@
       <c r="T4" s="0" t="n">
         <v>66.924001688</v>
       </c>
-      <c r="U4" s="0" t="n">
-        <v>4.25444</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>0.977913759946823</v>
@@ -647,16 +632,13 @@
       <c r="T5" s="0" t="n">
         <v>72.51495264</v>
       </c>
-      <c r="U5" s="0" t="n">
-        <v>4.57922</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>0.977560800552368</v>
@@ -712,16 +694,13 @@
       <c r="T6" s="0" t="n">
         <v>71.76525786</v>
       </c>
-      <c r="U6" s="0" t="n">
-        <v>4.31814</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>0.975713649272919</v>
@@ -777,16 +756,13 @@
       <c r="T7" s="0" t="n">
         <v>71.7794516</v>
       </c>
-      <c r="U7" s="0" t="n">
-        <v>4.70598</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>0.969394360780716</v>
@@ -842,16 +818,13 @@
       <c r="T8" s="0" t="n">
         <v>63.719978248</v>
       </c>
-      <c r="U8" s="0" t="n">
-        <v>4.10152</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>0.970717397212982</v>
@@ -907,16 +880,13 @@
       <c r="T9" s="0" t="n">
         <v>62.377109736</v>
       </c>
-      <c r="U9" s="0" t="n">
-        <v>4.52146</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>0.968677790641785</v>
@@ -972,16 +942,13 @@
       <c r="T10" s="0" t="n">
         <v>69.9466461071429</v>
       </c>
-      <c r="U10" s="0" t="n">
-        <v>4.16516</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>0.96788569021225</v>
@@ -1037,16 +1004,13 @@
       <c r="T11" s="0" t="n">
         <v>69.4755780277778</v>
       </c>
-      <c r="U11" s="0" t="n">
-        <v>4.38924</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>0.966691303253174</v>
@@ -1102,16 +1066,13 @@
       <c r="T12" s="0" t="n">
         <v>71.4145339166667</v>
       </c>
-      <c r="U12" s="0" t="n">
-        <v>4.45594</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>0.972857913017273</v>
@@ -1167,16 +1128,13 @@
       <c r="T13" s="0" t="n">
         <v>76.3829176944445</v>
       </c>
-      <c r="U13" s="0" t="n">
-        <v>4.51522</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>0.971995336532593</v>
@@ -1232,16 +1190,13 @@
       <c r="T14" s="0" t="n">
         <v>74.5514765992064</v>
       </c>
-      <c r="U14" s="0" t="n">
-        <v>4.00372</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>0.971410652160644</v>
@@ -1297,16 +1252,13 @@
       <c r="T15" s="0" t="n">
         <v>73.0740168134921</v>
       </c>
-      <c r="U15" s="0" t="n">
-        <v>4.7234</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>0.964729960680008</v>
@@ -1362,16 +1314,13 @@
       <c r="T16" s="0" t="n">
         <v>67.5303479722222</v>
       </c>
-      <c r="U16" s="0" t="n">
-        <v>4.48662</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>0.960887416601181</v>
@@ -1427,16 +1376,13 @@
       <c r="T17" s="0" t="n">
         <v>62.1597953571429</v>
       </c>
-      <c r="U17" s="0" t="n">
-        <v>4.07032</v>
-      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>0.85454950594902</v>
@@ -1492,16 +1438,13 @@
       <c r="T18" s="0" t="n">
         <v>47.759976792</v>
       </c>
-      <c r="U18" s="0" t="n">
-        <v>2.19854</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>0.861526947021484</v>
@@ -1557,16 +1500,13 @@
       <c r="T19" s="0" t="n">
         <v>47.592663276</v>
       </c>
-      <c r="U19" s="0" t="n">
-        <v>2.27446</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>0.847097085952759</v>
@@ -1622,16 +1562,13 @@
       <c r="T20" s="0" t="n">
         <v>34.933740808</v>
       </c>
-      <c r="U20" s="0" t="n">
-        <v>2.00446</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>0.864082272291184</v>
@@ -1687,16 +1624,13 @@
       <c r="T21" s="0" t="n">
         <v>49.083009944</v>
       </c>
-      <c r="U21" s="0" t="n">
-        <v>3.90852</v>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>0.868130578279495</v>
@@ -1752,16 +1686,13 @@
       <c r="T22" s="0" t="n">
         <v>49.094255712</v>
       </c>
-      <c r="U22" s="0" t="n">
-        <v>2.28626</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>0.843515498161316</v>
@@ -1817,16 +1748,13 @@
       <c r="T23" s="0" t="n">
         <v>24.573701</v>
       </c>
-      <c r="U23" s="0" t="n">
-        <v>2.23266</v>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>0.869286975622177</v>
@@ -1882,16 +1810,13 @@
       <c r="T24" s="0" t="n">
         <v>51.769681692</v>
       </c>
-      <c r="U24" s="0" t="n">
-        <v>4.53034</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>0.86553085064888</v>
@@ -1947,16 +1872,13 @@
       <c r="T25" s="0" t="n">
         <v>48.95638396</v>
       </c>
-      <c r="U25" s="0" t="n">
-        <v>4.75704</v>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>0.920766231536865</v>
@@ -2012,16 +1934,13 @@
       <c r="T26" s="0" t="n">
         <v>59.777922716</v>
       </c>
-      <c r="U26" s="0" t="n">
-        <v>2.6667</v>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>0.922594581127167</v>
@@ -2077,16 +1996,13 @@
       <c r="T27" s="0" t="n">
         <v>61.258744512</v>
       </c>
-      <c r="U27" s="0" t="n">
-        <v>2.42594</v>
-      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>0.916530047416687</v>
@@ -2142,16 +2058,13 @@
       <c r="T28" s="0" t="n">
         <v>56.705417824</v>
       </c>
-      <c r="U28" s="0" t="n">
-        <v>2.0037</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>0.924923731088638</v>
@@ -2207,16 +2120,13 @@
       <c r="T29" s="0" t="n">
         <v>61.919133192</v>
       </c>
-      <c r="U29" s="0" t="n">
-        <v>2.874</v>
-      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>0.932205121278763</v>
@@ -2272,16 +2182,13 @@
       <c r="T30" s="0" t="n">
         <v>65.998080712</v>
       </c>
-      <c r="U30" s="0" t="n">
-        <v>3.64184</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>0.932457804679871</v>
@@ -2337,16 +2244,13 @@
       <c r="T31" s="0" t="n">
         <v>65.373110232</v>
       </c>
-      <c r="U31" s="0" t="n">
-        <v>3.7507</v>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>0.930714341402054</v>
@@ -2402,16 +2306,13 @@
       <c r="T32" s="0" t="n">
         <v>62.968055856</v>
       </c>
-      <c r="U32" s="0" t="n">
-        <v>3.88334</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>0.925005593061447</v>
@@ -2467,16 +2368,13 @@
       <c r="T33" s="0" t="n">
         <v>60.162092656</v>
       </c>
-      <c r="U33" s="0" t="n">
-        <v>3.60002</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>0.854341006278992</v>
@@ -2532,16 +2430,13 @@
       <c r="T34" s="0" t="n">
         <v>28.2908454791667</v>
       </c>
-      <c r="U34" s="0" t="n">
-        <v>1.94408</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>0.848409084727367</v>
@@ -2597,16 +2492,13 @@
       <c r="T35" s="0" t="n">
         <v>26.6862677041667</v>
       </c>
-      <c r="U35" s="0" t="n">
-        <v>1.61596</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>0.837198193868001</v>
@@ -2662,16 +2554,13 @@
       <c r="T36" s="0" t="n">
         <v>18.4615838208333</v>
       </c>
-      <c r="U36" s="0" t="n">
-        <v>1.78672</v>
-      </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>0.864883562674125</v>
@@ -2727,16 +2616,13 @@
       <c r="T37" s="0" t="n">
         <v>30.0111761708333</v>
       </c>
-      <c r="U37" s="0" t="n">
-        <v>2.14518</v>
-      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>0.862682407100995</v>
@@ -2792,16 +2678,13 @@
       <c r="T38" s="0" t="n">
         <v>24.3408826833333</v>
       </c>
-      <c r="U38" s="0" t="n">
-        <v>2.2637</v>
-      </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>0.871213296800852</v>
@@ -2857,16 +2740,13 @@
       <c r="T39" s="0" t="n">
         <v>23.5293024666667</v>
       </c>
-      <c r="U39" s="0" t="n">
-        <v>2.20296</v>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>0.863203772902489</v>
@@ -2922,16 +2802,13 @@
       <c r="T40" s="0" t="n">
         <v>23.4728770166667</v>
       </c>
-      <c r="U40" s="0" t="n">
-        <v>1.82856</v>
-      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>0.86329293474555</v>
@@ -2987,16 +2864,13 @@
       <c r="T41" s="0" t="n">
         <v>23.4940855625</v>
       </c>
-      <c r="U41" s="0" t="n">
-        <v>2.09824</v>
-      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>0.924601045449575</v>
@@ -3052,16 +2926,13 @@
       <c r="T42" s="0" t="n">
         <v>58.2862844766667</v>
       </c>
-      <c r="U42" s="0" t="n">
-        <v>3.38484</v>
-      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>0.923420781493187</v>
@@ -3117,16 +2988,13 @@
       <c r="T43" s="0" t="n">
         <v>58.51022622</v>
       </c>
-      <c r="U43" s="0" t="n">
-        <v>3.33636</v>
-      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>0.904382139841716</v>
@@ -3182,16 +3050,13 @@
       <c r="T44" s="0" t="n">
         <v>49.2923922466667</v>
       </c>
-      <c r="U44" s="0" t="n">
-        <v>2.67004</v>
-      </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>0.930618416070938</v>
@@ -3247,16 +3112,13 @@
       <c r="T45" s="0" t="n">
         <v>60.09791893</v>
       </c>
-      <c r="U45" s="0" t="n">
-        <v>3.43338</v>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>0.934511292775472</v>
@@ -3312,16 +3174,13 @@
       <c r="T46" s="0" t="n">
         <v>58.85228968</v>
       </c>
-      <c r="U46" s="0" t="n">
-        <v>3.10488</v>
-      </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>0.938678526679675</v>
@@ -3377,16 +3236,13 @@
       <c r="T47" s="0" t="n">
         <v>61.95266968</v>
       </c>
-      <c r="U47" s="0" t="n">
-        <v>3.64004</v>
-      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>0.906854853431384</v>
@@ -3442,16 +3298,13 @@
       <c r="T48" s="0" t="n">
         <v>45.89517368</v>
       </c>
-      <c r="U48" s="0" t="n">
-        <v>2.53672</v>
-      </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>0.922298530340195</v>
@@ -3507,16 +3360,13 @@
       <c r="T49" s="0" t="n">
         <v>51.09763668</v>
       </c>
-      <c r="U49" s="0" t="n">
-        <v>2.82332</v>
-      </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>0.908659688234329</v>
@@ -3572,16 +3422,13 @@
       <c r="T50" s="0" t="n">
         <v>51.8354989366667</v>
       </c>
-      <c r="U50" s="0" t="n">
-        <v>2.88262</v>
-      </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>0.907300311525663</v>
@@ -3637,16 +3484,13 @@
       <c r="T51" s="0" t="n">
         <v>49.8279588033334</v>
       </c>
-      <c r="U51" s="0" t="n">
-        <v>2.92216</v>
-      </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>0.897659026583036</v>
@@ -3702,16 +3546,13 @@
       <c r="T52" s="0" t="n">
         <v>47.51383706</v>
       </c>
-      <c r="U52" s="0" t="n">
-        <v>2.16706</v>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>0.912118809421857</v>
@@ -3767,16 +3608,13 @@
       <c r="T53" s="0" t="n">
         <v>54.4566663166667</v>
       </c>
-      <c r="U53" s="0" t="n">
-        <v>2.82592</v>
-      </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>0.909476055900256</v>
@@ -3832,16 +3670,13 @@
       <c r="T54" s="0" t="n">
         <v>50.12637026</v>
       </c>
-      <c r="U54" s="0" t="n">
-        <v>3.28966</v>
-      </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>0.91467423915863</v>
@@ -3897,16 +3732,13 @@
       <c r="T55" s="0" t="n">
         <v>51.3752288</v>
       </c>
-      <c r="U55" s="0" t="n">
-        <v>3.22374</v>
-      </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>0.897992402116457</v>
@@ -3962,16 +3794,13 @@
       <c r="T56" s="0" t="n">
         <v>46.7370875666666</v>
       </c>
-      <c r="U56" s="0" t="n">
-        <v>2.62892</v>
-      </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>0.904389088749885</v>
@@ -4027,16 +3856,13 @@
       <c r="T57" s="0" t="n">
         <v>53.7079721266667</v>
       </c>
-      <c r="U57" s="0" t="n">
-        <v>2.86632</v>
-      </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>0.938745722969373</v>
@@ -4092,16 +3918,13 @@
       <c r="T58" s="0" t="n">
         <v>50.2507397433333</v>
       </c>
-      <c r="U58" s="0" t="n">
-        <v>3.96596</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>0.941029945214589</v>
@@ -4157,16 +3980,13 @@
       <c r="T59" s="0" t="n">
         <v>51.9958659433333</v>
       </c>
-      <c r="U59" s="0" t="n">
-        <v>3.69408</v>
-      </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>0.921257184346517</v>
@@ -4222,16 +4042,13 @@
       <c r="T60" s="0" t="n">
         <v>40.2163095733333</v>
       </c>
-      <c r="U60" s="0" t="n">
-        <v>3.06634</v>
-      </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>0.948094481825829</v>
@@ -4287,16 +4104,13 @@
       <c r="T61" s="0" t="n">
         <v>56.9224574433333</v>
       </c>
-      <c r="U61" s="0" t="n">
-        <v>3.66264</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>0.944243293205897</v>
@@ -4352,16 +4166,13 @@
       <c r="T62" s="0" t="n">
         <v>52.65649401</v>
       </c>
-      <c r="U62" s="0" t="n">
-        <v>3.61132</v>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>0.942126210133235</v>
@@ -4417,16 +4228,13 @@
       <c r="T63" s="0" t="n">
         <v>51.64852559</v>
       </c>
-      <c r="U63" s="0" t="n">
-        <v>3.66782</v>
-      </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>0.933199939529101</v>
@@ -4482,16 +4290,13 @@
       <c r="T64" s="0" t="n">
         <v>47.5701987166667</v>
       </c>
-      <c r="U64" s="0" t="n">
-        <v>3.5722</v>
-      </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>0.939048924644788</v>
@@ -4546,9 +4351,6 @@
       </c>
       <c r="T65" s="0" t="n">
         <v>49.4844953333333</v>
-      </c>
-      <c r="U65" s="0" t="n">
-        <v>3.33112</v>
       </c>
     </row>
   </sheetData>
